--- a/src/file/sftzd.xlsx
+++ b/src/file/sftzd.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12420"/>
   </bookViews>
@@ -1364,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
@@ -1755,7 +1755,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.180555555555556" right="0.180555555555556" top="0.165277777777778" bottom="0.172916666666667" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="600"/>
+  <pageSetup paperSize="11" scale="92" fitToWidth="0" orientation="landscape" horizontalDpi="600"/>
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
